--- a/extenbooks/S709_extenbook.xlsx
+++ b/extenbooks/S709_extenbook.xlsx
@@ -17263,7 +17263,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -18621,11 +18621,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18648,112 +18648,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Figure 7.16 — US Industry ROP Deviations from Average, 1987–2005 (derivative of S705)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S709_research.json", "adequacy_report": "Technical/docs/chapters/CH7_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S709_DPR.md", "epr": "Technical/docs/series/S709_EPR.md", "loader": "Technical/code/L01_loaders/L01_S709_load.py", "processor": "Technical/code/P02_processors/P02_S709_construct.py", "validator": "Technical/code/V03_validators/V03_S709_validate.py", "processed": "Technical/data/processed/S709.parquet", "chopped_csv": "Technical/chopped/S709.csv", "extenbook_xlsx": "Technical/extenbooks/S709_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>subseries_ids</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>["S709-A"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>subsource_ids</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>["SHAIKH_2008_APPENDIX_7_2_ROP"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>content_type</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>time_series</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>extension_status</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>feasible_deferred</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S709_extenbook.xlsx
+++ b/extenbooks/S709_extenbook.xlsx
@@ -17210,7 +17210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A128"/>
+  <dimension ref="A1:A155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17403,7 +17403,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>| **S709-A** | 1987–2005 | Derived from S705 | rate deviation (decimal; industry ROP minus All-Private aggregate ROP) |</t>
+          <t>| **S709-A** (subseries — one data line within S709) | 1987–2005 | Derived from S705 | rate deviation (decimal; industry ROP minus All-Private aggregate ROP) |</t>
         </is>
       </c>
     </row>
@@ -17576,7 +17576,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>- **CD2 legacy ID**: `S035`</t>
+          <t>- **CD2 legacy ID** (identifier in CD2, the predecessor build of this dataset): `S035`</t>
         </is>
       </c>
     </row>
@@ -17593,7 +17593,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>## 9. Validation expectation</t>
+          <t>## Notation (plain-language key)</t>
         </is>
       </c>
     </row>
@@ -17603,99 +17603,99 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>Short forms used above, in plain language (this record is a downloadable external artifact):</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>- **S### / -A** — series identifiers in this project (e.g. S709); a trailing letter (e.g. S709-A) marks a *subseries* — one data line within that series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>- **DPR / EPR** — Data Provenance Record (this file) / Extension Provenance Record (its companion).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>- **Phase N** — Anu Framework pipeline stages: Phase 5 = ingestion, Phase 6 = extension, Phase 9 = visualization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>- **CD2** — the predecessor build of this dataset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>- **ROP** — (average) rate of profit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>- **IROP** — incremental rate of profit: the return on newly added capital (the year-to-year change in profit divided by the new investment that produced it).</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>- **MAE** — mean absolute error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
           <t>- **Tolerance**: ±0.5% per cell (derived content_type per playbook).</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>- **Expected MAE** against the xlsx `*_Deviation` columns: 0.0 (verbatim read).</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="4">
+    <row r="85">
+      <c r="A85" s="4">
         <f>== EPR: S709_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t># S709 — Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>**Series**: S709 — Figure 7.16 — US Industry ROP Deviations from Average, 1987–2005 (derivative of S705)</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>**Construction classification**: `formula` (one-line algebraic derivative of S705)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>**Extension method**: re-derive from S705 on any extension wave</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>**Authored**: 2026-05-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>**Author**: opus-subagent-ch7-fanout</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>**Related**: `S709_DPR.md`, `S705_EPR.md`</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr"/>
-    </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>## 1. Classification</t>
+          <t># S709 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
@@ -17705,37 +17705,49 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>`content_type = time_series`, `construction = formula`. Per the Anu rule:</t>
+          <t>**Series**: S709 — Figure 7.16 — US Industry ROP Deviations from Average, 1987–2005 (derivative of S705)</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr"/>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>**Phase**: 6 (Extension)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>&gt; "Growth-rate splice is ONLY valid when the original series was itself a directly-observed time series. If the original computed a formula, the extension must compute the same formula with extended component data."</t>
+          <t>**Construction classification**: `formula` (one-line algebraic derivative of S705)</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>**Extension method**: re-derive from S705 on any extension wave</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>This series is **formula**: it is the algebraic transform `dev_i,t = level_i,t − aggregate_t`. Therefore extension must re-fetch the underlying S705 components (BEA primaries) and re-compute the deviation; no growth-rate splice is permissible.</t>
+          <t>**Authored**: 2026-05-18</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>**Author**: opus-subagent-ch7-fanout</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>## 2. Method</t>
+          <t>**Related**: `S709_DPR.md`, `S705_EPR.md`</t>
         </is>
       </c>
     </row>
@@ -17745,106 +17757,98 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>INPUTS</t>
-        </is>
-      </c>
+      <c r="A97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">  S705's processed parquet (Technical/data/processed/S705.parquet)</t>
+          <t>## 1. Classification</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  All-Private aggregate column from S705</t>
-        </is>
-      </c>
+      <c r="A99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr"/>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>`content_type = time_series`, `construction = formula`. Per the Anu rule:</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>PROCEDURE (Phase 5, this wave)</t>
-        </is>
-      </c>
+      <c r="A101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">  L01: read Shaikh Appendix 7.2 xlsx (same xlsx as S705); extract *_Deviation / *_Dev columns</t>
+          <t>&gt; "Growth-rate splice is ONLY valid when the original series was itself a directly-observed time series. If the original computed a formula, the extension must compute the same formula with extended component data."</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  P02: union the deviation columns into long-form; emit data/processed/S709.parquet</t>
-        </is>
-      </c>
+      <c r="A103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">  V03: compare against xlsx; expect MAE ≈ 0</t>
+          <t>This series is **formula**: it is the algebraic transform `dev_i,t = level_i,t − aggregate_t`. Therefore extension must re-fetch the underlying S705 components (BEA (US Bureau of Economic Analysis) primaries) and re-compute the deviation; no growth-rate splice is permissible.</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>## 2. Method</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>The scripts named below are the per-series loader (`L01`), processor (`P02`), and validator (`V03`).</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
         <is>
           <t>```</t>
         </is>
       </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>## 3. Worked example</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>For year 1990, industry Chemicals in S709: `dev_Chemicals_1990 = ROP_Chemicals_1990 − ROP_AllPrivate_1990`. Shaikh's xlsx pre-computes this in the `Chemicals_Deviation` column; we read it directly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>## 4. No-Proxy disclosure</t>
+          <t>INPUTS</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr"/>
+      <c r="A112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  S705's processed parquet (Technical/data/processed/S705.parquet)</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>**None.**</t>
+          <t xml:space="preserve">  All-Private aggregate column from S705</t>
         </is>
       </c>
     </row>
@@ -17854,27 +17858,35 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>## 5. No-Synthetic disclosure</t>
+          <t>PROCEDURE (Phase 5, this wave)</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr"/>
+      <c r="A116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  L01: read Shaikh Appendix 7.2 xlsx (same xlsx as S705); extract *_Deviation / *_Dev columns</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>**None.**</t>
+          <t xml:space="preserve">  P02: union the deviation columns into long-form; emit data/processed/S709.parquet</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr"/>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  V03: compare against xlsx; expect MAE ≈ 0</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>## 6. Failure-mode table</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -17884,48 +17896,197 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>| Failure | Action |</t>
+          <t>## 3. Worked example</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
+          <t>For year 1990, industry Chemicals in S709: `dev_Chemicals_1990 = ROP_Chemicals_1990 − ROP_AllPrivate_1990`. Shaikh's xlsx pre-computes this in the `Chemicals_Deviation` column; we read it directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>## 4. No-Proxy disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>**None.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>## 5. No-Synthetic disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>**None.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>## 6. Failure-mode table</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>| Failure | Action |</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>|---|---|</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
           <t>| Source xlsx missing | Same as S705 (re-fetch from Wayback) |</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
+    <row r="138">
+      <c r="A138" t="inlineStr">
         <is>
           <t>| Deviation column missing for an industry | P02 logs warning, emits available subset |</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
         <is>
           <t>## 7. CD2 divergence pre-disclosure</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>CD2's `S035` used the same xlsx. RSCD's Phase 5 deliverable should match CD2 at MAE = 0 on the book period.</t>
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>CD2 (the predecessor build of this dataset) used the same xlsx for `S035`. RSCD's Phase 5 deliverable should match CD2 at MAE = 0 on the book period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>## Notation (plain-language key)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Short forms used above, in plain language (this record is a downloadable external artifact):</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>- **S###** — series identifiers in this project (e.g. S705, S709).</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>- **DPR / EPR** — Data Provenance Record / Extension Provenance Record (this file).</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>- **Phase N** — Anu Framework pipeline stages: Phase 5 = ingestion, Phase 6 = extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>- **L01 / P02 / V03** — the per-series load / process / validate scripts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>- **CD2** — the predecessor build of this dataset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>- **ROP** — (average) rate of profit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>- **BEA** — US Bureau of Economic Analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>- **MAE** — mean absolute error.</t>
         </is>
       </c>
     </row>
@@ -18523,7 +18684,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -18606,7 +18767,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-18T22:08:15.145165+00:00</t>
+          <t>2026-07-02T06:25:25.485931+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S709_extenbook.xlsx
+++ b/extenbooks/S709_extenbook.xlsx
@@ -18767,7 +18767,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-02T06:25:25.485931+00:00</t>
+          <t>2026-07-11T03:44:26.172935+00:00</t>
         </is>
       </c>
     </row>
@@ -18782,11 +18782,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18809,6 +18809,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_2008_APPENDIX_7_2_ROP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "fix-completed-then-publish", "reason": "Per-industry deviation of S705 average ROP from the All-Private benchmark (31 industries). Figure 7.16, source, and the '18 of 30 cross zero' finding verified verbatim against KB ch07. Fixed: research JSON name and year_range_book corrected 1988\u21921987 (Fig 7.16 is the ROP-deviation panel derived from S705, which starts 1987; chopped data confirms 1987\u20132005). DPR already carried the correct 1987\u20132005.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S709_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S709_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Decision 0004: Ch7 figure not covered by Phase 2 candidate list; ported from CD2 S035.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>rate deviation (decimal; industry ROP minus All-Private aggregate ROP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
